--- a/Testing_Reports/load_test_cases.xlsx
+++ b/Testing_Reports/load_test_cases.xlsx
@@ -504,7 +504,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated automatically during CI/CD Execution pipeline on 2026-08-29 12:46:08</t>
+          <t>Generated automatically during CI/CD Execution pipeline on 2026-08-29 14:36:01</t>
         </is>
       </c>
     </row>
